--- a/sheets/대금율보/검수/산조합주 중중모리.xlsx
+++ b/sheets/대금율보/검수/산조합주 중중모리.xlsx
@@ -14786,7 +14786,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌇‹</t>
+          <t xml:space="preserve">太⌇</t>
         </is>
       </c>
       <c r="C10" s="23"/>
@@ -14975,7 +14975,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C14" s="24"/>
@@ -14988,7 +14988,7 @@
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧)‹</t>
+          <t xml:space="preserve">南∧)</t>
         </is>
       </c>
       <c r="G14" s="24"/>
@@ -16069,16 +16069,12 @@
         </is>
       </c>
       <c r="C36" s="24"/>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D36" s="21"/>
       <c r="E36" s="24"/>
       <c r="F36" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△‹</t>
+△</t>
         </is>
       </c>
       <c r="G36" s="24"/>
@@ -16403,7 +16399,7 @@
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太⌇‹</t>
+          <t xml:space="preserve">太⌇</t>
         </is>
       </c>
       <c r="C42" s="24"/>
@@ -17148,7 +17144,7 @@
       <c r="O56" s="24"/>
       <c r="P56" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∧)‹</t>
+          <t xml:space="preserve">南∧)</t>
         </is>
       </c>
       <c r="Q56" s="24"/>
@@ -17543,11 +17539,7 @@
         </is>
       </c>
       <c r="S70" s="24"/>
-      <c r="T70" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="T70" s="21"/>
       <c r="U70" s="24"/>
     </row>
   </sheetData>

--- a/sheets/대금율보/검수/산조합주 중중모리.xlsx
+++ b/sheets/대금율보/검수/산조합주 중중모리.xlsx
@@ -14339,32 +14339,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="13.46" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="138.71" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="138.71" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="138.71" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="138.71" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="138.71" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -14670,7 +14670,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="138.71" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="138.71" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="138.71" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="U10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="138.71" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="138.71" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="138.71" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="138.71" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -15041,10 +15041,10 @@
       </c>
       <c r="U14" s="24"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="93.02" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="138.71" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="138.71" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
       </c>
       <c r="U18" s="23"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="138.71" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="138.71" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="138.71" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="U21" s="23"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="138.71" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="138.71" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -15473,7 +15473,7 @@
       </c>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="138.71" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="U24" s="23"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="138.71" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="138.71" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="138.71" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="U27" s="23"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="138.71" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -15744,10 +15744,10 @@
       </c>
       <c r="U28" s="24"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="93.02" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="138.71" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="21" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="138.71" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
       </c>
       <c r="U32" s="23"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="138.71" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21"/>
       <c r="C33" s="24"/>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="U33" s="24"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="138.71" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="21" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="138.71" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
       <c r="T35" s="21"/>
       <c r="U35" s="23"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="138.71" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
       </c>
       <c r="U36" s="24"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="138.71" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="138.71" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="U38" s="23"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="138.71" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
       <c r="T39" s="21"/>
       <c r="U39" s="24"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="138.71" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="21" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="138.71" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
       <c r="T41" s="21"/>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="138.71" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -16463,10 +16463,10 @@
       </c>
       <c r="U42" s="24"/>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="93.02" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -16493,7 +16493,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="138.71" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="138.71" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="U46" s="23"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="138.71" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
       <c r="T47" s="21"/>
       <c r="U47" s="24"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="138.71" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="138.71" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
       <c r="T49" s="21"/>
       <c r="U49" s="23"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="138.71" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="U50" s="24"/>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="138.71" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
       <c r="T51" s="21"/>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="138.71" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="U52" s="23"/>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="138.71" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="24"/>
@@ -16997,7 +16997,7 @@
       <c r="T53" s="21"/>
       <c r="U53" s="24"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="138.71" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="U54" s="22"/>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="138.71" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="23"/>
@@ -17091,7 +17091,7 @@
       <c r="T55" s="21"/>
       <c r="U55" s="23"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="138.71" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21" t="inlineStr">
         <is>
@@ -17162,10 +17162,10 @@
       </c>
       <c r="U56" s="24"/>
     </row>
-    <row r="57">
+    <row r="57" ht="6.0" customHeight="true">
       <c r="A57" s="0"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="93.02" customHeight="true">
       <c r="A58" s="0"/>
       <c r="B58" s="20" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
       <c r="T58" s="20"/>
       <c r="U58" s="20"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="138.71" customHeight="true">
       <c r="A59" s="0"/>
       <c r="B59" s="21"/>
       <c r="C59" s="22"/>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="U59" s="22"/>
     </row>
-    <row r="60" ht="56" customHeight="1">
+    <row r="60" ht="138.71" customHeight="true">
       <c r="A60" s="0"/>
       <c r="B60" s="21"/>
       <c r="C60" s="23"/>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="U60" s="23"/>
     </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="61" ht="138.71" customHeight="true">
       <c r="A61" s="0"/>
       <c r="B61" s="21"/>
       <c r="C61" s="24"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="U61" s="24"/>
     </row>
-    <row r="62" ht="56" customHeight="1">
+    <row r="62" ht="138.71" customHeight="true">
       <c r="A62" s="0"/>
       <c r="B62" s="21"/>
       <c r="C62" s="22"/>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="U62" s="22"/>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="138.71" customHeight="true">
       <c r="A63" s="0"/>
       <c r="B63" s="21"/>
       <c r="C63" s="23"/>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="U63" s="23"/>
     </row>
-    <row r="64" ht="56" customHeight="1">
+    <row r="64" ht="138.71" customHeight="true">
       <c r="A64" s="0"/>
       <c r="B64" s="21"/>
       <c r="C64" s="24"/>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="U64" s="24"/>
     </row>
-    <row r="65" ht="56" customHeight="1">
+    <row r="65" ht="138.71" customHeight="true">
       <c r="A65" s="0"/>
       <c r="B65" s="21"/>
       <c r="C65" s="22"/>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="U65" s="22"/>
     </row>
-    <row r="66" ht="56" customHeight="1">
+    <row r="66" ht="138.71" customHeight="true">
       <c r="A66" s="0"/>
       <c r="B66" s="21"/>
       <c r="C66" s="23"/>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="U66" s="23"/>
     </row>
-    <row r="67" ht="56" customHeight="1">
+    <row r="67" ht="138.71" customHeight="true">
       <c r="A67" s="0"/>
       <c r="B67" s="21"/>
       <c r="C67" s="24"/>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="U67" s="24"/>
     </row>
-    <row r="68" ht="56" customHeight="1">
+    <row r="68" ht="138.71" customHeight="true">
       <c r="A68" s="0"/>
       <c r="B68" s="21"/>
       <c r="C68" s="22"/>
@@ -17488,7 +17488,7 @@
       <c r="T68" s="21"/>
       <c r="U68" s="22"/>
     </row>
-    <row r="69" ht="56" customHeight="1">
+    <row r="69" ht="138.71" customHeight="true">
       <c r="A69" s="0"/>
       <c r="B69" s="21"/>
       <c r="C69" s="23"/>
@@ -17515,7 +17515,7 @@
       </c>
       <c r="U69" s="23"/>
     </row>
-    <row r="70" ht="56" customHeight="1">
+    <row r="70" ht="138.71" customHeight="true">
       <c r="A70" s="0"/>
       <c r="B70" s="21"/>
       <c r="C70" s="24"/>
@@ -17552,7 +17552,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
   <rowBreaks count="4" manualBreakCount="4">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
